--- a/Code_for_grid_world/python_version/assignment/assignment2/results/deterministic/policy_matrix_deterministic.xlsx
+++ b/Code_for_grid_world/python_version/assignment/assignment2/results/deterministic/policy_matrix_deterministic.xlsx
@@ -549,7 +549,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
